--- a/informes_data/Euroleague/2025-26/Regular_Season/individual/NP_play_by_play_EL_346_R35.xlsx
+++ b/informes_data/Euroleague/2025-26/Regular_Season/individual/NP_play_by_play_EL_346_R35.xlsx
@@ -553,7 +553,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>M. DIAKITE</t>
+          <t>G. RADZEVICIUS</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -565,73 +565,73 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>4.2844</v>
+        <v>3.8578</v>
       </c>
       <c r="E2" t="n">
-        <v>4.9235</v>
+        <v>2.4217</v>
       </c>
       <c r="F2" t="n">
-        <v>-0.639</v>
+        <v>1.4361</v>
       </c>
       <c r="G2" t="n">
-        <v>7.3153</v>
+        <v>1.4392</v>
       </c>
       <c r="H2" t="n">
-        <v>1.4766</v>
+        <v>0.8837</v>
       </c>
       <c r="I2" t="n">
-        <v>5.8387</v>
+        <v>0.5555</v>
       </c>
       <c r="J2" t="n">
-        <v>9.0562</v>
+        <v>1.3179</v>
       </c>
       <c r="K2" t="n">
-        <v>1.9529</v>
+        <v>0.6554</v>
       </c>
       <c r="L2" t="n">
-        <v>7.1034</v>
+        <v>0.6625</v>
       </c>
       <c r="M2" t="n">
-        <v>-1.7409</v>
+        <v>0.1213</v>
       </c>
       <c r="N2" t="n">
-        <v>-0.4762</v>
+        <v>0.2283</v>
       </c>
       <c r="O2" t="n">
-        <v>-1.2647</v>
+        <v>-0.107</v>
       </c>
       <c r="P2" t="n">
-        <v>-2.0876</v>
+        <v>1.3917</v>
       </c>
       <c r="Q2" t="n">
-        <v>-3.4793</v>
+        <v>0</v>
       </c>
       <c r="R2" t="n">
         <v>1.3917</v>
       </c>
       <c r="S2" t="n">
-        <v>0.5232</v>
+        <v>-0.0452</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.2592</v>
+        <v>0.0316</v>
       </c>
       <c r="U2" t="n">
-        <v>0.7824</v>
+        <v>-0.0769</v>
       </c>
       <c r="V2" t="n">
-        <v>-1.4665</v>
+        <v>1.0722</v>
       </c>
       <c r="W2" t="n">
-        <v>-0.3943</v>
+        <v>1.0722</v>
       </c>
       <c r="X2" t="n">
-        <v>-1.0722</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>T. LUWAWU-CABARROT</t>
+          <t>M. DIAKITE</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,73 +643,73 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>3.5375</v>
+        <v>3.77</v>
       </c>
       <c r="E3" t="n">
-        <v>2.4154</v>
+        <v>4.6443</v>
       </c>
       <c r="F3" t="n">
-        <v>1.1221</v>
+        <v>-0.8743</v>
       </c>
       <c r="G3" t="n">
-        <v>1.5978</v>
+        <v>7.3153</v>
       </c>
       <c r="H3" t="n">
-        <v>2.7189</v>
+        <v>1.4766</v>
       </c>
       <c r="I3" t="n">
-        <v>-1.1211</v>
+        <v>5.8387</v>
       </c>
       <c r="J3" t="n">
-        <v>2.7312</v>
+        <v>9.0562</v>
       </c>
       <c r="K3" t="n">
-        <v>3.2167</v>
+        <v>1.9529</v>
       </c>
       <c r="L3" t="n">
-        <v>-0.4855</v>
+        <v>7.1034</v>
       </c>
       <c r="M3" t="n">
-        <v>-1.1334</v>
+        <v>-1.7409</v>
       </c>
       <c r="N3" t="n">
-        <v>-0.4978</v>
+        <v>-0.4762</v>
       </c>
       <c r="O3" t="n">
-        <v>-0.6356000000000001</v>
+        <v>-1.2647</v>
       </c>
       <c r="P3" t="n">
-        <v>-2.3195</v>
+        <v>-2.0876</v>
       </c>
       <c r="Q3" t="n">
         <v>-3.4793</v>
       </c>
       <c r="R3" t="n">
-        <v>1.1598</v>
+        <v>1.3917</v>
       </c>
       <c r="S3" t="n">
-        <v>0.5065</v>
+        <v>0.008800000000000001</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.731</v>
+        <v>-0.5384</v>
       </c>
       <c r="U3" t="n">
-        <v>1.2375</v>
+        <v>0.5472</v>
       </c>
       <c r="V3" t="n">
-        <v>3.7527</v>
+        <v>-1.4665</v>
       </c>
       <c r="W3" t="n">
-        <v>3.8945</v>
+        <v>-0.3943</v>
       </c>
       <c r="X3" t="n">
-        <v>-0.1418</v>
+        <v>-1.0722</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>G. RADZEVICIUS</t>
+          <t>T. LUWAWU-CABARROT</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,67 +721,67 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>3.3785</v>
+        <v>3.7651</v>
       </c>
       <c r="E4" t="n">
-        <v>1.8752</v>
+        <v>3.0799</v>
       </c>
       <c r="F4" t="n">
-        <v>1.5033</v>
+        <v>0.6852</v>
       </c>
       <c r="G4" t="n">
-        <v>1.4392</v>
+        <v>1.5978</v>
       </c>
       <c r="H4" t="n">
-        <v>0.8837</v>
+        <v>2.7189</v>
       </c>
       <c r="I4" t="n">
-        <v>0.5555</v>
+        <v>-1.1211</v>
       </c>
       <c r="J4" t="n">
-        <v>1.3179</v>
+        <v>2.7312</v>
       </c>
       <c r="K4" t="n">
-        <v>0.6554</v>
+        <v>3.2167</v>
       </c>
       <c r="L4" t="n">
-        <v>0.6625</v>
+        <v>-0.4855</v>
       </c>
       <c r="M4" t="n">
-        <v>0.1213</v>
+        <v>-1.1334</v>
       </c>
       <c r="N4" t="n">
-        <v>0.2283</v>
+        <v>-0.4978</v>
       </c>
       <c r="O4" t="n">
-        <v>-0.107</v>
+        <v>-0.6356000000000001</v>
       </c>
       <c r="P4" t="n">
-        <v>1.3917</v>
+        <v>-2.3195</v>
       </c>
       <c r="Q4" t="n">
-        <v>0</v>
+        <v>-3.4793</v>
       </c>
       <c r="R4" t="n">
-        <v>1.3917</v>
+        <v>1.1598</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.5245</v>
+        <v>0.7341</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.5149</v>
+        <v>-0.06660000000000001</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.0097</v>
+        <v>0.8006</v>
       </c>
       <c r="V4" t="n">
-        <v>1.0722</v>
+        <v>3.7527</v>
       </c>
       <c r="W4" t="n">
-        <v>1.0722</v>
+        <v>3.8945</v>
       </c>
       <c r="X4" t="n">
-        <v>0</v>
+        <v>-0.1418</v>
       </c>
     </row>
     <row r="5">
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>3.0199</v>
+        <v>3.6433</v>
       </c>
       <c r="E5" t="n">
-        <v>5.4241</v>
+        <v>6.0138</v>
       </c>
       <c r="F5" t="n">
-        <v>-2.4041</v>
+        <v>-2.3705</v>
       </c>
       <c r="G5" t="n">
         <v>3.1494</v>
@@ -844,13 +844,13 @@
         <v>1.6237</v>
       </c>
       <c r="S5" t="n">
-        <v>-1.1294</v>
+        <v>-0.5061</v>
       </c>
       <c r="T5" t="n">
-        <v>-1.0297</v>
+        <v>-0.44</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.0997</v>
+        <v>-0.06610000000000001</v>
       </c>
       <c r="V5" t="n">
         <v>0.5361</v>
@@ -877,13 +877,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>-1.8646</v>
+        <v>-0.8305</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.0336</v>
+        <v>0.6308</v>
       </c>
       <c r="F6" t="n">
-        <v>-1.831</v>
+        <v>-1.4614</v>
       </c>
       <c r="G6" t="n">
         <v>-0.8925</v>
@@ -922,13 +922,13 @@
         <v>1.1598</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.9722</v>
+        <v>0.0619</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.8804</v>
+        <v>-0.2159</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.09180000000000001</v>
+        <v>0.2779</v>
       </c>
       <c r="V6" t="n">
         <v>0</v>
@@ -943,7 +943,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>M. NOWELL</t>
+          <t>R. VILLAR</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,73 +955,73 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-2.1277</v>
+        <v>-2.3151</v>
       </c>
       <c r="E7" t="n">
-        <v>0.8768</v>
+        <v>0.5712</v>
       </c>
       <c r="F7" t="n">
-        <v>-3.0045</v>
+        <v>-2.8863</v>
       </c>
       <c r="G7" t="n">
-        <v>-2.3295</v>
+        <v>-0.9153</v>
       </c>
       <c r="H7" t="n">
-        <v>-1.3323</v>
+        <v>-0.9855</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.9971</v>
+        <v>0.0702</v>
       </c>
       <c r="J7" t="n">
-        <v>-1.2532</v>
+        <v>1.0507</v>
       </c>
       <c r="K7" t="n">
-        <v>-0.4166</v>
+        <v>0.0336</v>
       </c>
       <c r="L7" t="n">
-        <v>-0.8366</v>
+        <v>1.0171</v>
       </c>
       <c r="M7" t="n">
-        <v>-1.0762</v>
+        <v>-1.966</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.9157</v>
+        <v>-1.0191</v>
       </c>
       <c r="O7" t="n">
-        <v>-0.1605</v>
+        <v>-0.9469</v>
       </c>
       <c r="P7" t="n">
-        <v>0.4639</v>
+        <v>0.6959</v>
       </c>
       <c r="Q7" t="n">
         <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>0.4639</v>
+        <v>0.6959</v>
       </c>
       <c r="S7" t="n">
-        <v>0.8101</v>
+        <v>-0.4874</v>
       </c>
       <c r="T7" t="n">
-        <v>1.0578</v>
+        <v>-0.4795</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.2478</v>
+        <v>-0.007900000000000001</v>
       </c>
       <c r="V7" t="n">
-        <v>-1.0722</v>
+        <v>-1.6083</v>
       </c>
       <c r="W7" t="n">
-        <v>1.0722</v>
+        <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>-2.1444</v>
+        <v>-1.6083</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>R. VILLAR</t>
+          <t>M. NOWELL</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,67 +1033,67 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-2.2986</v>
+        <v>-2.6606</v>
       </c>
       <c r="E8" t="n">
-        <v>0.4533</v>
+        <v>0.007900000000000001</v>
       </c>
       <c r="F8" t="n">
-        <v>-2.7519</v>
+        <v>-2.6684</v>
       </c>
       <c r="G8" t="n">
-        <v>-0.9153</v>
+        <v>-2.3295</v>
       </c>
       <c r="H8" t="n">
-        <v>-0.9855</v>
+        <v>-1.3323</v>
       </c>
       <c r="I8" t="n">
-        <v>0.0702</v>
+        <v>-0.9971</v>
       </c>
       <c r="J8" t="n">
-        <v>1.0507</v>
+        <v>-1.2532</v>
       </c>
       <c r="K8" t="n">
-        <v>0.0336</v>
+        <v>-0.4166</v>
       </c>
       <c r="L8" t="n">
-        <v>1.0171</v>
+        <v>-0.8366</v>
       </c>
       <c r="M8" t="n">
-        <v>-1.966</v>
+        <v>-1.0762</v>
       </c>
       <c r="N8" t="n">
-        <v>-1.0191</v>
+        <v>-0.9157</v>
       </c>
       <c r="O8" t="n">
-        <v>-0.9469</v>
+        <v>-0.1605</v>
       </c>
       <c r="P8" t="n">
-        <v>0.6959</v>
+        <v>0.4639</v>
       </c>
       <c r="Q8" t="n">
         <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>0.6959</v>
+        <v>0.4639</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.4709</v>
+        <v>0.2772</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.5975</v>
+        <v>0.1889</v>
       </c>
       <c r="U8" t="n">
-        <v>0.1265</v>
+        <v>0.0883</v>
       </c>
       <c r="V8" t="n">
-        <v>-1.6083</v>
+        <v>-1.0722</v>
       </c>
       <c r="W8" t="n">
-        <v>0</v>
+        <v>1.0722</v>
       </c>
       <c r="X8" t="n">
-        <v>-1.6083</v>
+        <v>-2.1444</v>
       </c>
     </row>
     <row r="9">
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-3.5123</v>
+        <v>-3.4952</v>
       </c>
       <c r="E9" t="n">
-        <v>-1.6252</v>
+        <v>-1.5072</v>
       </c>
       <c r="F9" t="n">
-        <v>-1.8871</v>
+        <v>-1.988</v>
       </c>
       <c r="G9" t="n">
         <v>-1.1973</v>
@@ -1156,13 +1156,13 @@
         <v>0</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.083</v>
+        <v>-0.0659</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.4481</v>
+        <v>-0.3301</v>
       </c>
       <c r="U9" t="n">
-        <v>0.3651</v>
+        <v>0.2642</v>
       </c>
       <c r="V9" t="n">
         <v>-1.0722</v>
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-4.6092</v>
+        <v>-5.5535</v>
       </c>
       <c r="E10" t="n">
-        <v>0.7405</v>
+        <v>-0.439</v>
       </c>
       <c r="F10" t="n">
-        <v>-5.3497</v>
+        <v>-5.1145</v>
       </c>
       <c r="G10" t="n">
         <v>-5.8476</v>
@@ -1234,13 +1234,13 @@
         <v>1.3917</v>
       </c>
       <c r="S10" t="n">
-        <v>1.0064</v>
+        <v>0.0622</v>
       </c>
       <c r="T10" t="n">
-        <v>1.4787</v>
+        <v>0.2992</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.4722</v>
+        <v>-0.237</v>
       </c>
       <c r="V10" t="n">
         <v>0</v>
@@ -1267,22 +1267,22 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-0.1921000000000026</v>
+        <v>0.1813000000000002</v>
       </c>
       <c r="E11" t="n">
-        <v>15.05</v>
+        <v>15.4234</v>
       </c>
       <c r="F11" t="n">
-        <v>-15.2419</v>
+        <v>-15.2421</v>
       </c>
       <c r="G11" t="n">
         <v>2.3195</v>
       </c>
       <c r="H11" t="n">
-        <v>-1.8961</v>
+        <v>-1.896099999999999</v>
       </c>
       <c r="I11" t="n">
-        <v>4.215599999999999</v>
+        <v>4.215600000000001</v>
       </c>
       <c r="J11" t="n">
         <v>19.7105</v>
@@ -1300,7 +1300,7 @@
         <v>-7.6384</v>
       </c>
       <c r="O11" t="n">
-        <v>-9.752600000000001</v>
+        <v>-9.752599999999999</v>
       </c>
       <c r="P11" t="n">
         <v>-2.3195</v>
@@ -1312,16 +1312,16 @@
         <v>9.2782</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.3337999999999999</v>
+        <v>0.03959999999999999</v>
       </c>
       <c r="T11" t="n">
-        <v>-1.9243</v>
+        <v>-1.5508</v>
       </c>
       <c r="U11" t="n">
         <v>1.5903</v>
       </c>
       <c r="V11" t="n">
-        <v>0.1417999999999995</v>
+        <v>0.1418000000000004</v>
       </c>
       <c r="W11" t="n">
         <v>8.8612</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>7.4535</v>
+        <v>8.1669</v>
       </c>
       <c r="E12" t="n">
-        <v>9.352600000000001</v>
+        <v>9.942399999999999</v>
       </c>
       <c r="F12" t="n">
-        <v>-1.8992</v>
+        <v>-1.7755</v>
       </c>
       <c r="G12" t="n">
         <v>5.5176</v>
@@ -1390,13 +1390,13 @@
         <v>1.3917</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.0461</v>
+        <v>0.6673</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.6721</v>
+        <v>-0.0824</v>
       </c>
       <c r="U12" t="n">
-        <v>0.626</v>
+        <v>0.7497</v>
       </c>
       <c r="V12" t="n">
         <v>1.7501</v>
@@ -1411,7 +1411,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>W. TAVARES</t>
+          <t>G. DECK</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1423,73 +1423,73 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>2.6518</v>
+        <v>1.7934</v>
       </c>
       <c r="E13" t="n">
-        <v>2.3837</v>
+        <v>1.8565</v>
       </c>
       <c r="F13" t="n">
-        <v>0.2681</v>
+        <v>-0.0631</v>
       </c>
       <c r="G13" t="n">
-        <v>1.3849</v>
+        <v>-0.3343</v>
       </c>
       <c r="H13" t="n">
-        <v>2.6362</v>
+        <v>-0.3745</v>
       </c>
       <c r="I13" t="n">
-        <v>-1.2512</v>
+        <v>0.0402</v>
       </c>
       <c r="J13" t="n">
-        <v>3.3897</v>
+        <v>1.1743</v>
       </c>
       <c r="K13" t="n">
-        <v>3.0585</v>
+        <v>0.7093</v>
       </c>
       <c r="L13" t="n">
-        <v>0.3312</v>
+        <v>0.465</v>
       </c>
       <c r="M13" t="n">
-        <v>-2.0048</v>
+        <v>-1.5086</v>
       </c>
       <c r="N13" t="n">
-        <v>-0.4223</v>
+        <v>-1.0838</v>
       </c>
       <c r="O13" t="n">
-        <v>-1.5825</v>
+        <v>-0.4248</v>
       </c>
       <c r="P13" t="n">
-        <v>-2.0876</v>
+        <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>-3.4793</v>
+        <v>-1.1598</v>
       </c>
       <c r="R13" t="n">
-        <v>1.3917</v>
+        <v>1.1598</v>
       </c>
       <c r="S13" t="n">
-        <v>4.0323</v>
+        <v>-0.0167</v>
       </c>
       <c r="T13" t="n">
-        <v>2.4732</v>
+        <v>-0.3025</v>
       </c>
       <c r="U13" t="n">
-        <v>1.5591</v>
+        <v>0.2858</v>
       </c>
       <c r="V13" t="n">
-        <v>-0.6778999999999999</v>
+        <v>2.1444</v>
       </c>
       <c r="W13" t="n">
-        <v>0</v>
+        <v>2.1444</v>
       </c>
       <c r="X13" t="n">
-        <v>-0.6778999999999999</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>G. DECK</t>
+          <t>W. TAVARES</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1501,73 +1501,73 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>1.7649</v>
+        <v>0.2833</v>
       </c>
       <c r="E14" t="n">
-        <v>1.9745</v>
+        <v>0.4965</v>
       </c>
       <c r="F14" t="n">
-        <v>-0.2096</v>
+        <v>-0.2132</v>
       </c>
       <c r="G14" t="n">
-        <v>-0.3343</v>
+        <v>1.3849</v>
       </c>
       <c r="H14" t="n">
-        <v>-0.3745</v>
+        <v>2.6362</v>
       </c>
       <c r="I14" t="n">
-        <v>0.0402</v>
+        <v>-1.2512</v>
       </c>
       <c r="J14" t="n">
-        <v>1.1743</v>
+        <v>3.3897</v>
       </c>
       <c r="K14" t="n">
-        <v>0.7093</v>
+        <v>3.0585</v>
       </c>
       <c r="L14" t="n">
-        <v>0.465</v>
+        <v>0.3312</v>
       </c>
       <c r="M14" t="n">
-        <v>-1.5086</v>
+        <v>-2.0048</v>
       </c>
       <c r="N14" t="n">
-        <v>-1.0838</v>
+        <v>-0.4223</v>
       </c>
       <c r="O14" t="n">
-        <v>-0.4248</v>
+        <v>-1.5825</v>
       </c>
       <c r="P14" t="n">
-        <v>0</v>
+        <v>-2.0876</v>
       </c>
       <c r="Q14" t="n">
-        <v>-1.1598</v>
+        <v>-3.4793</v>
       </c>
       <c r="R14" t="n">
-        <v>1.1598</v>
+        <v>1.3917</v>
       </c>
       <c r="S14" t="n">
-        <v>-0.0452</v>
+        <v>1.6639</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.1845</v>
+        <v>0.586</v>
       </c>
       <c r="U14" t="n">
-        <v>0.1393</v>
+        <v>1.0778</v>
       </c>
       <c r="V14" t="n">
-        <v>2.1444</v>
+        <v>-0.6778999999999999</v>
       </c>
       <c r="W14" t="n">
-        <v>2.1444</v>
+        <v>0</v>
       </c>
       <c r="X14" t="n">
-        <v>0</v>
+        <v>-0.6778999999999999</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>T. MALEDON</t>
+          <t>S. LLULL</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,64 +1579,64 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>-0.342</v>
+        <v>-0.027</v>
       </c>
       <c r="E15" t="n">
-        <v>-0.6898</v>
+        <v>0.7103</v>
       </c>
       <c r="F15" t="n">
-        <v>0.3477</v>
+        <v>-0.7373</v>
       </c>
       <c r="G15" t="n">
-        <v>-0.667</v>
+        <v>0.1843</v>
       </c>
       <c r="H15" t="n">
-        <v>0.0323</v>
+        <v>-1.7094</v>
       </c>
       <c r="I15" t="n">
-        <v>-0.6993</v>
+        <v>1.8936</v>
       </c>
       <c r="J15" t="n">
-        <v>-0.6417</v>
+        <v>1.9643</v>
       </c>
       <c r="K15" t="n">
-        <v>0.1078</v>
+        <v>-0.6687</v>
       </c>
       <c r="L15" t="n">
-        <v>-0.7495000000000001</v>
+        <v>2.633</v>
       </c>
       <c r="M15" t="n">
-        <v>-0.0252</v>
+        <v>-1.78</v>
       </c>
       <c r="N15" t="n">
-        <v>-0.0755</v>
+        <v>-1.0406</v>
       </c>
       <c r="O15" t="n">
-        <v>0.0502</v>
+        <v>-0.7393999999999999</v>
       </c>
       <c r="P15" t="n">
-        <v>-0.232</v>
+        <v>-0.4639</v>
       </c>
       <c r="Q15" t="n">
         <v>-1.1598</v>
       </c>
       <c r="R15" t="n">
-        <v>0.9278</v>
+        <v>0.6959</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.5153</v>
+        <v>0.2526</v>
       </c>
       <c r="T15" t="n">
-        <v>0.0395</v>
+        <v>-0.09420000000000001</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.5548</v>
+        <v>0.3468</v>
       </c>
       <c r="V15" t="n">
-        <v>1.0722</v>
+        <v>0</v>
       </c>
       <c r="W15" t="n">
-        <v>1.0722</v>
+        <v>0</v>
       </c>
       <c r="X15" t="n">
         <v>0</v>
@@ -1645,7 +1645,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>S. LLULL</t>
+          <t>T. MALEDON</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,64 +1657,64 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>-0.8406</v>
+        <v>-0.3033</v>
       </c>
       <c r="E16" t="n">
-        <v>0.3564</v>
+        <v>-1.0436</v>
       </c>
       <c r="F16" t="n">
-        <v>-1.1971</v>
+        <v>0.7403</v>
       </c>
       <c r="G16" t="n">
-        <v>0.1843</v>
+        <v>-0.667</v>
       </c>
       <c r="H16" t="n">
-        <v>-1.7094</v>
+        <v>0.0323</v>
       </c>
       <c r="I16" t="n">
-        <v>1.8936</v>
+        <v>-0.6993</v>
       </c>
       <c r="J16" t="n">
-        <v>1.9643</v>
+        <v>-0.6417</v>
       </c>
       <c r="K16" t="n">
-        <v>-0.6687</v>
+        <v>0.1078</v>
       </c>
       <c r="L16" t="n">
-        <v>2.633</v>
+        <v>-0.7495000000000001</v>
       </c>
       <c r="M16" t="n">
-        <v>-1.78</v>
+        <v>-0.0252</v>
       </c>
       <c r="N16" t="n">
-        <v>-1.0406</v>
+        <v>-0.0755</v>
       </c>
       <c r="O16" t="n">
-        <v>-0.7393999999999999</v>
+        <v>0.0502</v>
       </c>
       <c r="P16" t="n">
-        <v>-0.4639</v>
+        <v>-0.232</v>
       </c>
       <c r="Q16" t="n">
         <v>-1.1598</v>
       </c>
       <c r="R16" t="n">
-        <v>0.6959</v>
+        <v>0.9278</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.5610000000000001</v>
+        <v>-0.4766</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.4481</v>
+        <v>-0.3143</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.1129</v>
+        <v>-0.1623</v>
       </c>
       <c r="V16" t="n">
-        <v>0</v>
+        <v>1.0722</v>
       </c>
       <c r="W16" t="n">
-        <v>0</v>
+        <v>1.0722</v>
       </c>
       <c r="X16" t="n">
         <v>0</v>
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-1.0652</v>
+        <v>-0.4189</v>
       </c>
       <c r="E17" t="n">
-        <v>2.8132</v>
+        <v>3.4029</v>
       </c>
       <c r="F17" t="n">
-        <v>-3.8783</v>
+        <v>-3.8219</v>
       </c>
       <c r="G17" t="n">
         <v>-0.5951</v>
@@ -1780,13 +1780,13 @@
         <v>1.3917</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.0242</v>
+        <v>0.6221</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.8215</v>
+        <v>-0.2317</v>
       </c>
       <c r="U17" t="n">
-        <v>0.7973</v>
+        <v>0.8538</v>
       </c>
       <c r="V17" t="n">
         <v>-0.6778999999999999</v>
@@ -1801,7 +1801,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A. FELIZ</t>
+          <t>C. OKEKE</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,73 +1813,73 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-1.2075</v>
+        <v>-0.7867</v>
       </c>
       <c r="E18" t="n">
-        <v>-1.7391</v>
+        <v>0.7675999999999999</v>
       </c>
       <c r="F18" t="n">
-        <v>0.5315</v>
+        <v>-1.5543</v>
       </c>
       <c r="G18" t="n">
-        <v>-1.1772</v>
+        <v>-1.7735</v>
       </c>
       <c r="H18" t="n">
-        <v>-1.4383</v>
+        <v>1.4753</v>
       </c>
       <c r="I18" t="n">
-        <v>0.261</v>
+        <v>-3.2489</v>
       </c>
       <c r="J18" t="n">
-        <v>-1.2163</v>
+        <v>0.9993</v>
       </c>
       <c r="K18" t="n">
-        <v>-1.2163</v>
+        <v>1.2471</v>
       </c>
       <c r="L18" t="n">
-        <v>0</v>
+        <v>-0.2477</v>
       </c>
       <c r="M18" t="n">
-        <v>0.0391</v>
+        <v>-2.7729</v>
       </c>
       <c r="N18" t="n">
-        <v>-0.222</v>
+        <v>0.2283</v>
       </c>
       <c r="O18" t="n">
-        <v>0.261</v>
+        <v>-3.0012</v>
       </c>
       <c r="P18" t="n">
-        <v>0.6959</v>
+        <v>2.0876</v>
       </c>
       <c r="Q18" t="n">
         <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>0.6959</v>
+        <v>2.0876</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.7262</v>
+        <v>-0.0286</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.5228</v>
+        <v>-0.2317</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.2034</v>
+        <v>0.2032</v>
       </c>
       <c r="V18" t="n">
-        <v>0</v>
+        <v>-1.0722</v>
       </c>
       <c r="W18" t="n">
         <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>0</v>
+        <v>-1.0722</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>C. OKEKE</t>
+          <t>A. FELIZ</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,67 +1891,67 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-1.6346</v>
+        <v>-0.848</v>
       </c>
       <c r="E19" t="n">
-        <v>0.1778</v>
+        <v>-1.5032</v>
       </c>
       <c r="F19" t="n">
-        <v>-1.8124</v>
+        <v>0.6552</v>
       </c>
       <c r="G19" t="n">
-        <v>-1.7735</v>
+        <v>-1.1772</v>
       </c>
       <c r="H19" t="n">
-        <v>1.4753</v>
+        <v>-1.4383</v>
       </c>
       <c r="I19" t="n">
-        <v>-3.2489</v>
+        <v>0.261</v>
       </c>
       <c r="J19" t="n">
-        <v>0.9993</v>
+        <v>-1.2163</v>
       </c>
       <c r="K19" t="n">
-        <v>1.2471</v>
+        <v>-1.2163</v>
       </c>
       <c r="L19" t="n">
-        <v>-0.2477</v>
+        <v>0</v>
       </c>
       <c r="M19" t="n">
-        <v>-2.7729</v>
+        <v>0.0391</v>
       </c>
       <c r="N19" t="n">
-        <v>0.2283</v>
+        <v>-0.222</v>
       </c>
       <c r="O19" t="n">
-        <v>-3.0012</v>
+        <v>0.261</v>
       </c>
       <c r="P19" t="n">
-        <v>2.0876</v>
+        <v>0.6959</v>
       </c>
       <c r="Q19" t="n">
         <v>0</v>
       </c>
       <c r="R19" t="n">
-        <v>2.0876</v>
+        <v>0.6959</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.8764</v>
+        <v>-0.3666</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.8215</v>
+        <v>-0.2869</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.0549</v>
+        <v>-0.07969999999999999</v>
       </c>
       <c r="V19" t="n">
-        <v>-1.0722</v>
+        <v>0</v>
       </c>
       <c r="W19" t="n">
         <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>-1.0722</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-1.9215</v>
+        <v>-2.0001</v>
       </c>
       <c r="E20" t="n">
-        <v>2.1175</v>
+        <v>1.8816</v>
       </c>
       <c r="F20" t="n">
-        <v>-4.039</v>
+        <v>-3.8817</v>
       </c>
       <c r="G20" t="n">
         <v>-1.1742</v>
@@ -2014,13 +2014,13 @@
         <v>0.9278</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.0668</v>
+        <v>-0.1454</v>
       </c>
       <c r="T20" t="n">
-        <v>0.1142</v>
+        <v>-0.1217</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.181</v>
+        <v>-0.0237</v>
       </c>
       <c r="V20" t="n">
         <v>-1.6083</v>
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-4.6667</v>
+        <v>-4.0947</v>
       </c>
       <c r="E21" t="n">
-        <v>-2.041</v>
+        <v>-1.8051</v>
       </c>
       <c r="F21" t="n">
-        <v>-2.6257</v>
+        <v>-2.2896</v>
       </c>
       <c r="G21" t="n">
         <v>-3.685</v>
@@ -2092,13 +2092,13 @@
         <v>0.9278</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.8373</v>
+        <v>-0.2653</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.7468</v>
+        <v>-0.5109</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.0905</v>
+        <v>0.2456</v>
       </c>
       <c r="V21" t="n">
         <v>-1.0722</v>
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>0.1920999999999999</v>
+        <v>1.764900000000001</v>
       </c>
       <c r="E22" t="n">
-        <v>14.7058</v>
+        <v>14.7059</v>
       </c>
       <c r="F22" t="n">
-        <v>-14.514</v>
+        <v>-12.9411</v>
       </c>
       <c r="G22" t="n">
         <v>-2.319500000000001</v>
@@ -2170,16 +2170,16 @@
         <v>11.5977</v>
       </c>
       <c r="S22" t="n">
-        <v>0.3338000000000002</v>
+        <v>1.9067</v>
       </c>
       <c r="T22" t="n">
-        <v>-1.5904</v>
+        <v>-1.5903</v>
       </c>
       <c r="U22" t="n">
-        <v>1.9242</v>
+        <v>3.497</v>
       </c>
       <c r="V22" t="n">
-        <v>-0.1417999999999997</v>
+        <v>-0.1418000000000006</v>
       </c>
       <c r="W22" t="n">
         <v>8.183299999999999</v>
